--- a/forms/trg/Formulir_TRG_swcerg.xlsx
+++ b/forms/trg/Formulir_TRG_swcerg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!B5:B24)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,31 +913,39 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Syahrial Sabaniah, S.TP., MT.</t>
+          <t>Prof.Dr. Suhardi, S.TP., MP.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Instrumentation and Control</t>
+          <t>Water Resources Engineering and Management</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2596-6763</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6008038</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57202443954</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof.Dr.Ir. Sitti Nur Faridah, MP.</t>
+          <t>Syahrial Sabaniah, S.TP., MT.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Soil and Water Engineering</t>
+          <t>Instrumentation and Control</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof.Dr.Ir. Ahmad Munir, M.Eng</t>
+          <t>Prof.Dr.Ir. Sitti Nur Faridah, MP.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +1010,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Water Resources Engineering &amp; Management</t>
+          <t>Soil and Water Engineering</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,22 +1032,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhamad Askari</t>
+          <t>Prof.Dr.Ir. Ahmad Munir, M.Eng</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Malaysia Sabah University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Water Management</t>
+          <t>Water Resources Engineering &amp; Management</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,22 +1069,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Reskiana Saefuddin, Ph.D</t>
+          <t>Dr. Muhamad Askari</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>BRIN</t>
+          <t>Malaysia Sabah University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Smart Irrigation</t>
+          <t>Agricultural Water Management</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,20 +1106,24 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muh. Adriansyah Musliadi</t>
+          <t>Reskiana Saefuddin, Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n"/>
+          <t>BRIN</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Smart Irrigation</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1131,12 +1143,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Andi Nurul Khatimah</t>
+          <t>Muh. Adriansyah Musliadi</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1162,10 +1174,26 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Andi Nurul Khatimah</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Soil and water conservation is the application of engineering and biological principles to the solution of soil and water management problems. The conservation of natural resources implies utilization without waste while maintaining a continuous profitable level of crop production and while improving environmental quality. It this, necessary to develop economical systems that meet these requirement</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1173,7 +1201,11 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1362,15 +1394,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
